--- a/Thesis_result_figure/RAW_SA_experiment/12_4_1.0_200.xlsx
+++ b/Thesis_result_figure/RAW_SA_experiment/12_4_1.0_200.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1bs\lyhbs\dfjsp_ppo_\Thesis_result_figure\RAW_SA_experiment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12490737-6906-490F-99F2-B12915DF16E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="win rate" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,7 @@
     <sheet name="maximum" sheetId="4" r:id="rId4"/>
     <sheet name="before win rate" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -41,12 +47,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -54,17 +60,37 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -91,27 +117,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -149,7 +188,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -183,6 +222,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -217,9 +257,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -392,11 +433,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -437,16 +478,17 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>97866</v>
       </c>
@@ -486,7 +528,7 @@
         <v>61000</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>85751</v>
       </c>
@@ -506,7 +548,7 @@
         <v>71162</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>105952</v>
       </c>
@@ -526,7 +568,7 @@
         <v>69997</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>82546</v>
       </c>
@@ -546,7 +588,7 @@
         <v>74239</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>81968</v>
       </c>
@@ -566,7 +608,7 @@
         <v>61840</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>61555</v>
       </c>
@@ -586,7 +628,7 @@
         <v>43345</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>83637</v>
       </c>
@@ -606,7 +648,7 @@
         <v>56376</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>106699</v>
       </c>
@@ -626,7 +668,7 @@
         <v>63848</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>76611</v>
       </c>
@@ -646,7 +688,7 @@
         <v>48179</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>65252</v>
       </c>
@@ -666,7 +708,7 @@
         <v>56708</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>67096</v>
       </c>
@@ -686,7 +728,7 @@
         <v>59950</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>79854</v>
       </c>
@@ -706,7 +748,7 @@
         <v>68434</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>79462</v>
       </c>
@@ -726,7 +768,7 @@
         <v>66433</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>73098</v>
       </c>
@@ -746,7 +788,7 @@
         <v>59428</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>98561</v>
       </c>
@@ -766,7 +808,7 @@
         <v>59092</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>71594</v>
       </c>
@@ -786,7 +828,7 @@
         <v>62654</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>96648</v>
       </c>
@@ -806,7 +848,7 @@
         <v>63742</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>76615</v>
       </c>
@@ -826,7 +868,7 @@
         <v>57048</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>98760</v>
       </c>
@@ -846,7 +888,7 @@
         <v>44190</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>92868</v>
       </c>
@@ -866,7 +908,7 @@
         <v>57379</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>94923</v>
       </c>
@@ -886,7 +928,7 @@
         <v>66652</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>106150</v>
       </c>
@@ -906,7 +948,7 @@
         <v>69707</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>78207</v>
       </c>
@@ -926,7 +968,7 @@
         <v>66880</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>80555</v>
       </c>
@@ -946,7 +988,7 @@
         <v>64048</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>81172</v>
       </c>
@@ -966,7 +1008,7 @@
         <v>50959</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>78166</v>
       </c>
@@ -986,7 +1028,7 @@
         <v>66467</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>66969</v>
       </c>
@@ -1006,7 +1048,7 @@
         <v>67018</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>81477</v>
       </c>
@@ -1026,7 +1068,7 @@
         <v>63234</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>85653</v>
       </c>
@@ -1046,7 +1088,7 @@
         <v>62316</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>83057</v>
       </c>
@@ -1066,7 +1108,7 @@
         <v>61530</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>85738</v>
       </c>
@@ -1086,7 +1128,7 @@
         <v>64200</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>86825</v>
       </c>
@@ -1106,7 +1148,7 @@
         <v>49674</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>70600</v>
       </c>
@@ -1126,7 +1168,7 @@
         <v>60720</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>63447</v>
       </c>
@@ -1146,7 +1188,7 @@
         <v>65010</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>98485</v>
       </c>
@@ -1166,7 +1208,7 @@
         <v>44035</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>77948</v>
       </c>
@@ -1186,7 +1228,7 @@
         <v>52020</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>82451</v>
       </c>
@@ -1206,7 +1248,7 @@
         <v>53827</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>86163</v>
       </c>
@@ -1226,7 +1268,7 @@
         <v>62675</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>55607</v>
       </c>
@@ -1246,7 +1288,7 @@
         <v>54470</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>83545</v>
       </c>
@@ -1266,7 +1308,7 @@
         <v>58444</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>94148</v>
       </c>
@@ -1286,7 +1328,7 @@
         <v>66421</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>72275</v>
       </c>
@@ -1306,7 +1348,7 @@
         <v>63828</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>80370</v>
       </c>
@@ -1326,7 +1368,7 @@
         <v>54317</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>99059</v>
       </c>
@@ -1346,7 +1388,7 @@
         <v>62859</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>86744</v>
       </c>
@@ -1366,7 +1408,7 @@
         <v>68386</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>93717</v>
       </c>
@@ -1386,7 +1428,7 @@
         <v>73650</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>79439</v>
       </c>
@@ -1406,7 +1448,7 @@
         <v>50921</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>81209</v>
       </c>
@@ -1426,7 +1468,7 @@
         <v>58759</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>99746</v>
       </c>
@@ -1446,7 +1488,7 @@
         <v>66354</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>83120</v>
       </c>
@@ -1466,17 +1508,44 @@
         <v>58894</v>
       </c>
     </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <f>AVERAGE(A2:A51)</f>
+        <v>83587.16</v>
+      </c>
+      <c r="B52" s="2">
+        <f t="shared" ref="B52:F52" si="0">AVERAGE(B2:B51)</f>
+        <v>67431.399999999994</v>
+      </c>
+      <c r="C52" s="2">
+        <f t="shared" si="0"/>
+        <v>66772.2</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="0"/>
+        <v>63289.02</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="0"/>
+        <v>83904.24</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="0"/>
+        <v>60666.38</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1496,255 +1565,255 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.9052132701421801</v>
+        <v>0.90521327014218012</v>
       </c>
       <c r="B2">
         <v>0.863849765258216</v>
       </c>
       <c r="C2">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="D2">
-        <v>0.9760765550239234</v>
+        <v>0.97607655502392343</v>
       </c>
       <c r="E2">
-        <v>0.966824644549763</v>
+        <v>0.96682464454976302</v>
       </c>
       <c r="F2">
         <v>0.863849765258216</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.9665071770334929</v>
+        <v>0.96650717703349287</v>
       </c>
       <c r="B3">
-        <v>0.7962085308056872</v>
+        <v>0.79620853080568721</v>
       </c>
       <c r="C3">
-        <v>0.9473684210526315</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="D3">
-        <v>0.9715639810426541</v>
+        <v>0.97156398104265407</v>
       </c>
       <c r="E3">
-        <v>0.9043062200956937</v>
+        <v>0.90430622009569372</v>
       </c>
       <c r="F3">
         <v>0.863849765258216</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.9674418604651163</v>
+        <v>0.96744186046511627</v>
       </c>
       <c r="B4">
-        <v>0.8497652582159625</v>
+        <v>0.84976525821596249</v>
       </c>
       <c r="C4">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="D4">
-        <v>0.9674418604651163</v>
+        <v>0.96744186046511627</v>
       </c>
       <c r="E4">
-        <v>0.9234449760765551</v>
+        <v>0.92344497607655507</v>
       </c>
       <c r="F4">
-        <v>0.8544600938967136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0.85446009389671362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.9004739336492891</v>
+        <v>0.90047393364928907</v>
       </c>
       <c r="B5">
-        <v>0.8672985781990521</v>
+        <v>0.86729857819905209</v>
       </c>
       <c r="C5">
-        <v>0.8755980861244019</v>
+        <v>0.87559808612440193</v>
       </c>
       <c r="D5">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="E5">
-        <v>0.9146919431279621</v>
+        <v>0.91469194312796209</v>
       </c>
       <c r="F5">
-        <v>0.8720379146919431</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.87203791469194314</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.8815165876777251</v>
+        <v>0.88151658767772512</v>
       </c>
       <c r="B6">
-        <v>0.8720379146919431</v>
+        <v>0.87203791469194314</v>
       </c>
       <c r="C6">
-        <v>0.9241706161137441</v>
+        <v>0.92417061611374407</v>
       </c>
       <c r="D6">
-        <v>0.937799043062201</v>
+        <v>0.93779904306220097</v>
       </c>
       <c r="E6">
         <v>0.9061032863849765</v>
       </c>
       <c r="F6">
-        <v>0.861244019138756</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>0.86124401913875603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.8578199052132701</v>
+        <v>0.85781990521327012</v>
       </c>
       <c r="B7">
-        <v>0.8530805687203792</v>
+        <v>0.85308056872037918</v>
       </c>
       <c r="C7">
-        <v>0.9282296650717703</v>
+        <v>0.92822966507177029</v>
       </c>
       <c r="D7">
         <v>0.971830985915493</v>
       </c>
       <c r="E7">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="F7">
-        <v>0.8151658767772512</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0.81516587677725116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.9521531100478469</v>
+        <v>0.95215311004784686</v>
       </c>
       <c r="B8">
-        <v>0.8851674641148325</v>
+        <v>0.88516746411483249</v>
       </c>
       <c r="C8">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="D8">
         <v>0.9712918660287081</v>
       </c>
       <c r="E8">
-        <v>0.92018779342723</v>
+        <v>0.92018779342723001</v>
       </c>
       <c r="F8">
-        <v>0.8544600938967136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>0.85446009389671362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.9765258215962441</v>
+        <v>0.97652582159624413</v>
       </c>
       <c r="B9">
-        <v>0.8483412322274881</v>
+        <v>0.84834123222748814</v>
       </c>
       <c r="C9">
-        <v>0.9760765550239234</v>
+        <v>0.97607655502392343</v>
       </c>
       <c r="D9">
-        <v>0.9720930232558139</v>
+        <v>0.97209302325581393</v>
       </c>
       <c r="E9">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="F9">
-        <v>0.8325581395348837</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>0.83255813953488367</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.9295774647887324</v>
+        <v>0.92957746478873238</v>
       </c>
       <c r="B10">
-        <v>0.9090909090909091</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="C10">
         <v>0.976303317535545</v>
       </c>
       <c r="D10">
-        <v>0.9812206572769953</v>
+        <v>0.98122065727699526</v>
       </c>
       <c r="E10">
-        <v>0.9248826291079812</v>
+        <v>0.92488262910798125</v>
       </c>
       <c r="F10">
-        <v>0.855072463768116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>0.85507246376811596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="B11">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="C11">
-        <v>0.9052132701421801</v>
+        <v>0.90521327014218012</v>
       </c>
       <c r="D11">
-        <v>0.9248826291079812</v>
+        <v>0.92488262910798125</v>
       </c>
       <c r="E11">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="F11">
-        <v>0.8732394366197183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>0.87323943661971826</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="B12">
-        <v>0.8755980861244019</v>
+        <v>0.87559808612440193</v>
       </c>
       <c r="C12">
-        <v>0.919431279620853</v>
+        <v>0.91943127962085303</v>
       </c>
       <c r="D12">
-        <v>0.957345971563981</v>
+        <v>0.95734597156398105</v>
       </c>
       <c r="E12">
-        <v>0.919431279620853</v>
+        <v>0.91943127962085303</v>
       </c>
       <c r="F12">
-        <v>0.8436018957345972</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>0.84360189573459721</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>0.9478672985781991</v>
+        <v>0.94786729857819907</v>
       </c>
       <c r="B13">
-        <v>0.8403755868544601</v>
+        <v>0.84037558685446012</v>
       </c>
       <c r="C13">
-        <v>0.919431279620853</v>
+        <v>0.91943127962085303</v>
       </c>
       <c r="D13">
-        <v>0.9330143540669856</v>
+        <v>0.93301435406698563</v>
       </c>
       <c r="E13">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="F13">
-        <v>0.8625592417061612</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>0.86255924170616116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.95260663507109</v>
       </c>
       <c r="B14">
-        <v>0.8421052631578947</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="C14">
-        <v>0.957345971563981</v>
+        <v>0.95734597156398105</v>
       </c>
       <c r="D14">
         <v>0.9569377990430622</v>
@@ -1753,390 +1822,390 @@
         <v>0.892018779342723</v>
       </c>
       <c r="F14">
-        <v>0.8957345971563981</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>0.89573459715639814</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="B15">
-        <v>0.8277511961722488</v>
+        <v>0.82775119617224879</v>
       </c>
       <c r="C15">
-        <v>0.981042654028436</v>
+        <v>0.98104265402843605</v>
       </c>
       <c r="D15">
-        <v>0.9186602870813397</v>
+        <v>0.91866028708133973</v>
       </c>
       <c r="E15">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="F15">
         <v>0.8651162790697674</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.9859154929577465</v>
       </c>
       <c r="B16">
-        <v>0.84688995215311</v>
+        <v>0.84688995215311003</v>
       </c>
       <c r="C16">
-        <v>0.9620853080568721</v>
+        <v>0.96208530805687209</v>
       </c>
       <c r="D16">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="E16">
-        <v>0.9521531100478469</v>
+        <v>0.95215311004784686</v>
       </c>
       <c r="F16">
-        <v>0.8372093023255814</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>0.83720930232558144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>0.9186602870813397</v>
+        <v>0.91866028708133973</v>
       </c>
       <c r="B17">
-        <v>0.8502415458937198</v>
+        <v>0.85024154589371981</v>
       </c>
       <c r="C17">
-        <v>0.9295774647887324</v>
+        <v>0.92957746478873238</v>
       </c>
       <c r="D17">
         <v>0.976303317535545</v>
       </c>
       <c r="E17">
-        <v>0.8697674418604651</v>
+        <v>0.86976744186046506</v>
       </c>
       <c r="F17">
-        <v>0.8815165876777251</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>0.88151658767772512</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>0.9624413145539906</v>
+        <v>0.96244131455399062</v>
       </c>
       <c r="B18">
-        <v>0.8164251207729468</v>
+        <v>0.81642512077294682</v>
       </c>
       <c r="C18">
         <v>0.892018779342723</v>
       </c>
       <c r="D18">
-        <v>0.9530516431924883</v>
+        <v>0.95305164319248825</v>
       </c>
       <c r="E18">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="F18">
-        <v>0.8483412322274881</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>0.84834123222748814</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>0.8851674641148325</v>
+        <v>0.88516746411483249</v>
       </c>
       <c r="B19">
-        <v>0.8516746411483254</v>
+        <v>0.85167464114832536</v>
       </c>
       <c r="C19">
-        <v>0.9478672985781991</v>
+        <v>0.94786729857819907</v>
       </c>
       <c r="D19">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="E19">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="F19">
-        <v>0.8325581395348837</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>0.83255813953488367</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>0.927536231884058</v>
+        <v>0.92753623188405798</v>
       </c>
       <c r="B20">
-        <v>0.8578199052132701</v>
+        <v>0.85781990521327012</v>
       </c>
       <c r="C20">
-        <v>0.9289099526066351</v>
+        <v>0.92890995260663511</v>
       </c>
       <c r="D20">
-        <v>0.9234449760765551</v>
+        <v>0.92344497607655507</v>
       </c>
       <c r="E20">
-        <v>0.8530805687203792</v>
+        <v>0.85308056872037918</v>
       </c>
       <c r="F20">
-        <v>0.812206572769953</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>0.81220657276995301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>0.9282296650717703</v>
+        <v>0.92822966507177029</v>
       </c>
       <c r="B21">
-        <v>0.8516746411483254</v>
+        <v>0.85167464114832536</v>
       </c>
       <c r="C21">
-        <v>0.9521531100478469</v>
+        <v>0.95215311004784686</v>
       </c>
       <c r="D21">
-        <v>0.9720930232558139</v>
+        <v>0.97209302325581393</v>
       </c>
       <c r="E21">
-        <v>0.9521531100478469</v>
+        <v>0.95215311004784686</v>
       </c>
       <c r="F21">
-        <v>0.8578199052132701</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>0.85781990521327012</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>0.9620853080568721</v>
+        <v>0.96208530805687209</v>
       </c>
       <c r="B22">
-        <v>0.7703349282296651</v>
+        <v>0.77033492822966509</v>
       </c>
       <c r="C22">
-        <v>0.9530516431924883</v>
+        <v>0.95305164319248825</v>
       </c>
       <c r="D22">
-        <v>0.9146919431279621</v>
+        <v>0.91469194312796209</v>
       </c>
       <c r="E22">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="F22">
-        <v>0.8873239436619719</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>0.88732394366197187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>0.9581395348837209</v>
+        <v>0.95813953488372094</v>
       </c>
       <c r="B23">
-        <v>0.8388625592417062</v>
+        <v>0.83886255924170616</v>
       </c>
       <c r="C23">
         <v>0.9425837320574163</v>
       </c>
       <c r="D23">
-        <v>0.995260663507109</v>
+        <v>0.99526066350710896</v>
       </c>
       <c r="E23">
-        <v>0.9521531100478469</v>
+        <v>0.95215311004784686</v>
       </c>
       <c r="F23">
-        <v>0.8436018957345972</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>0.84360189573459721</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>0.9389671361502347</v>
+        <v>0.93896713615023475</v>
       </c>
       <c r="B24">
-        <v>0.861244019138756</v>
+        <v>0.86124401913875603</v>
       </c>
       <c r="C24">
-        <v>0.9323671497584541</v>
+        <v>0.93236714975845414</v>
       </c>
       <c r="D24">
-        <v>0.9665071770334929</v>
+        <v>0.96650717703349287</v>
       </c>
       <c r="E24">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="F24">
-        <v>0.8516746411483254</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>0.85167464114832536</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>0.919431279620853</v>
+        <v>0.91943127962085303</v>
       </c>
       <c r="B25">
-        <v>0.8356807511737089</v>
+        <v>0.83568075117370888</v>
       </c>
       <c r="C25">
-        <v>0.9282296650717703</v>
+        <v>0.92822966507177029</v>
       </c>
       <c r="D25">
-        <v>0.966824644549763</v>
+        <v>0.96682464454976302</v>
       </c>
       <c r="E25">
         <v>0.9061032863849765</v>
       </c>
       <c r="F25">
-        <v>0.8578199052132701</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>0.85781990521327012</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>0.957345971563981</v>
+        <v>0.95734597156398105</v>
       </c>
       <c r="B26">
-        <v>0.8421052631578947</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="C26">
-        <v>0.9624413145539906</v>
+        <v>0.96244131455399062</v>
       </c>
       <c r="D26">
         <v>0.976303317535545</v>
       </c>
       <c r="E26">
-        <v>0.9014084507042254</v>
+        <v>0.90140845070422537</v>
       </c>
       <c r="F26">
-        <v>0.8199052132701422</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>0.81990521327014221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.9178743961352657</v>
+        <v>0.91787439613526567</v>
       </c>
       <c r="B27">
-        <v>0.9082125603864735</v>
+        <v>0.90821256038647347</v>
       </c>
       <c r="C27">
-        <v>0.9241706161137441</v>
+        <v>0.92417061611374407</v>
       </c>
       <c r="D27">
-        <v>0.957345971563981</v>
+        <v>0.95734597156398105</v>
       </c>
       <c r="E27">
         <v>0.9371980676328503</v>
       </c>
       <c r="F27">
-        <v>0.8625592417061612</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>0.86255924170616116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>0.9289099526066351</v>
+        <v>0.92890995260663511</v>
       </c>
       <c r="B28">
-        <v>0.8803827751196173</v>
+        <v>0.88038277511961727</v>
       </c>
       <c r="C28">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="D28">
-        <v>0.9330143540669856</v>
+        <v>0.93301435406698563</v>
       </c>
       <c r="E28">
-        <v>0.9330143540669856</v>
+        <v>0.93301435406698563</v>
       </c>
       <c r="F28">
         <v>0.9138755980861244</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="B29">
-        <v>0.8293838862559242</v>
+        <v>0.82938388625592419</v>
       </c>
       <c r="C29">
-        <v>0.9665071770334929</v>
+        <v>0.96650717703349287</v>
       </c>
       <c r="D29">
-        <v>0.9671361502347418</v>
+        <v>0.96713615023474175</v>
       </c>
       <c r="E29">
-        <v>0.8815165876777251</v>
+        <v>0.88151658767772512</v>
       </c>
       <c r="F29">
-        <v>0.8851674641148325</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>0.88516746411483249</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.9569377990430622</v>
       </c>
       <c r="B30">
-        <v>0.8625592417061612</v>
+        <v>0.86255924170616116</v>
       </c>
       <c r="C30">
-        <v>0.9904306220095693</v>
+        <v>0.99043062200956933</v>
       </c>
       <c r="D30">
-        <v>0.9617224880382775</v>
+        <v>0.96172248803827753</v>
       </c>
       <c r="E30">
-        <v>0.919431279620853</v>
+        <v>0.91943127962085303</v>
       </c>
       <c r="F30">
-        <v>0.8647342995169082</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>0.86473429951690817</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.9425837320574163</v>
       </c>
       <c r="B31">
-        <v>0.8708133971291866</v>
+        <v>0.87081339712918659</v>
       </c>
       <c r="C31">
-        <v>0.9146919431279621</v>
+        <v>0.91469194312796209</v>
       </c>
       <c r="D31">
         <v>0.9425837320574163</v>
       </c>
       <c r="E31">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="F31">
-        <v>0.8685446009389671</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>0.86854460093896713</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>0.981042654028436</v>
+        <v>0.98104265402843605</v>
       </c>
       <c r="B32">
-        <v>0.909952606635071</v>
+        <v>0.90995260663507105</v>
       </c>
       <c r="C32">
-        <v>0.9330143540669856</v>
+        <v>0.93301435406698563</v>
       </c>
       <c r="D32">
-        <v>0.9478672985781991</v>
+        <v>0.94786729857819907</v>
       </c>
       <c r="E32">
-        <v>0.9295774647887324</v>
+        <v>0.92957746478873238</v>
       </c>
       <c r="F32">
-        <v>0.8755980861244019</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>0.87559808612440193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.9712918660287081</v>
       </c>
       <c r="B33">
-        <v>0.8732394366197183</v>
+        <v>0.87323943661971826</v>
       </c>
       <c r="C33">
-        <v>0.966824644549763</v>
+        <v>0.96682464454976302</v>
       </c>
       <c r="D33">
-        <v>0.9330143540669856</v>
+        <v>0.93301435406698563</v>
       </c>
       <c r="E33">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="F33">
-        <v>0.8591549295774648</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>0.85915492957746475</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.95260663507109</v>
       </c>
@@ -2144,369 +2213,370 @@
         <v>0.8564593301435407</v>
       </c>
       <c r="C34">
-        <v>0.966824644549763</v>
+        <v>0.96682464454976302</v>
       </c>
       <c r="D34">
-        <v>0.9617224880382775</v>
+        <v>0.96172248803827753</v>
       </c>
       <c r="E34">
-        <v>0.8909952606635071</v>
+        <v>0.89099526066350709</v>
       </c>
       <c r="F34">
-        <v>0.8957345971563981</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>0.89573459715639814</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0.957345971563981</v>
+        <v>0.95734597156398105</v>
       </c>
       <c r="B35">
-        <v>0.8450704225352113</v>
+        <v>0.84507042253521125</v>
       </c>
       <c r="C35">
-        <v>0.9389671361502347</v>
+        <v>0.93896713615023475</v>
       </c>
       <c r="D35">
-        <v>0.9473684210526315</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="E35">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="F35">
-        <v>0.9004739336492891</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>0.90047393364928907</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>0.957345971563981</v>
+        <v>0.95734597156398105</v>
       </c>
       <c r="B36">
-        <v>0.9107981220657277</v>
+        <v>0.91079812206572774</v>
       </c>
       <c r="C36">
-        <v>0.9241706161137441</v>
+        <v>0.92417061611374407</v>
       </c>
       <c r="D36">
-        <v>0.9248826291079812</v>
+        <v>0.92488262910798125</v>
       </c>
       <c r="E36">
-        <v>0.8967136150234741</v>
+        <v>0.89671361502347413</v>
       </c>
       <c r="F36">
-        <v>0.8151658767772512</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>0.81516587677725116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="B37">
-        <v>0.8229665071770335</v>
+        <v>0.82296650717703346</v>
       </c>
       <c r="C37">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="D37">
-        <v>0.9627906976744186</v>
+        <v>0.96279069767441861</v>
       </c>
       <c r="E37">
-        <v>0.9014084507042254</v>
+        <v>0.90140845070422537</v>
       </c>
       <c r="F37">
-        <v>0.8862559241706162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>0.88625592417061616</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.95260663507109</v>
       </c>
       <c r="B38">
-        <v>0.821256038647343</v>
+        <v>0.82125603864734298</v>
       </c>
       <c r="C38">
-        <v>0.8803827751196173</v>
+        <v>0.88038277511961727</v>
       </c>
       <c r="D38">
-        <v>0.9808612440191388</v>
+        <v>0.98086124401913877</v>
       </c>
       <c r="E38">
-        <v>0.8967136150234741</v>
+        <v>0.89671361502347413</v>
       </c>
       <c r="F38">
-        <v>0.8767772511848341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>0.87677725118483407</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>0.9530516431924883</v>
+        <v>0.95305164319248825</v>
       </c>
       <c r="B39">
-        <v>0.8957345971563981</v>
+        <v>0.89573459715639814</v>
       </c>
       <c r="C39">
-        <v>0.9530516431924883</v>
+        <v>0.95305164319248825</v>
       </c>
       <c r="D39">
-        <v>0.9565217391304348</v>
+        <v>0.95652173913043481</v>
       </c>
       <c r="E39">
-        <v>0.9162790697674419</v>
+        <v>0.91627906976744189</v>
       </c>
       <c r="F39">
-        <v>0.8873239436619719</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>0.88732394366197187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>0.8483412322274881</v>
+        <v>0.84834123222748814</v>
       </c>
       <c r="B40">
-        <v>0.8803827751196173</v>
+        <v>0.88038277511961727</v>
       </c>
       <c r="C40">
-        <v>0.9330143540669856</v>
+        <v>0.93301435406698563</v>
       </c>
       <c r="D40">
-        <v>0.9473684210526315</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="E40">
-        <v>0.9282296650717703</v>
+        <v>0.92822966507177029</v>
       </c>
       <c r="F40">
-        <v>0.8743961352657005</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>0.87439613526570048</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="B41">
-        <v>0.8625592417061612</v>
+        <v>0.86255924170616116</v>
       </c>
       <c r="C41">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="D41">
-        <v>0.937799043062201</v>
+        <v>0.93779904306220097</v>
       </c>
       <c r="E41">
-        <v>0.9052132701421801</v>
+        <v>0.90521327014218012</v>
       </c>
       <c r="F41">
-        <v>0.8436018957345972</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>0.84360189573459721</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>0.981042654028436</v>
+        <v>0.98104265402843605</v>
       </c>
       <c r="B42">
-        <v>0.8262910798122066</v>
+        <v>0.82629107981220662</v>
       </c>
       <c r="C42">
-        <v>0.9248826291079812</v>
+        <v>0.92488262910798125</v>
       </c>
       <c r="D42">
-        <v>0.9904306220095693</v>
+        <v>0.99043062200956933</v>
       </c>
       <c r="E42">
-        <v>0.909952606635071</v>
+        <v>0.90995260663507105</v>
       </c>
       <c r="F42">
-        <v>0.8862559241706162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>0.88625592417061616</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>0.9420289855072463</v>
+        <v>0.94202898550724634</v>
       </c>
       <c r="B43">
-        <v>0.8851674641148325</v>
+        <v>0.88516746411483249</v>
       </c>
       <c r="C43">
-        <v>0.9624413145539906</v>
+        <v>0.96244131455399062</v>
       </c>
       <c r="D43">
-        <v>0.9289099526066351</v>
+        <v>0.92890995260663511</v>
       </c>
       <c r="E43">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="F43">
-        <v>0.8873239436619719</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>0.88732394366197187</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>0.9090909090909091</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="B44">
-        <v>0.8465116279069768</v>
+        <v>0.84651162790697676</v>
       </c>
       <c r="C44">
         <v>0.95260663507109</v>
       </c>
       <c r="D44">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="E44">
-        <v>0.9154929577464789</v>
+        <v>0.91549295774647887</v>
       </c>
       <c r="F44">
-        <v>0.8578199052132701</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>0.85781990521327012</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>0.9627906976744186</v>
+        <v>0.96279069767441861</v>
       </c>
       <c r="B45">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="C45">
-        <v>0.9516908212560387</v>
+        <v>0.95169082125603865</v>
       </c>
       <c r="D45">
-        <v>0.9488372093023256</v>
+        <v>0.94883720930232562</v>
       </c>
       <c r="E45">
-        <v>0.9323671497584541</v>
+        <v>0.93236714975845414</v>
       </c>
       <c r="F45">
-        <v>0.8792270531400966</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>0.87922705314009664</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>0.9052132701421801</v>
+        <v>0.90521327014218012</v>
       </c>
       <c r="B46">
         <v>0.8564593301435407</v>
       </c>
       <c r="C46">
-        <v>0.9289099526066351</v>
+        <v>0.92890995260663511</v>
       </c>
       <c r="D46">
         <v>0.971830985915493</v>
       </c>
       <c r="E46">
-        <v>0.9090909090909091</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="F46">
-        <v>0.8325358851674641</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>0.83253588516746413</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>0.981042654028436</v>
+        <v>0.98104265402843605</v>
       </c>
       <c r="B47">
-        <v>0.8815165876777251</v>
+        <v>0.88151658767772512</v>
       </c>
       <c r="C47">
-        <v>0.937799043062201</v>
+        <v>0.93779904306220097</v>
       </c>
       <c r="D47">
-        <v>0.9488372093023256</v>
+        <v>0.94883720930232562</v>
       </c>
       <c r="E47">
-        <v>0.9342723004694836</v>
+        <v>0.93427230046948362</v>
       </c>
       <c r="F47">
-        <v>0.8976744186046511</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>0.89767441860465114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>0.9186602870813397</v>
+        <v>0.91866028708133973</v>
       </c>
       <c r="B48">
-        <v>0.8483412322274881</v>
+        <v>0.84834123222748814</v>
       </c>
       <c r="C48">
-        <v>0.9383886255924171</v>
+        <v>0.93838862559241709</v>
       </c>
       <c r="D48">
-        <v>0.957345971563981</v>
+        <v>0.95734597156398105</v>
       </c>
       <c r="E48">
-        <v>0.9323671497584541</v>
+        <v>0.93236714975845414</v>
       </c>
       <c r="F48">
-        <v>0.8544600938967136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>0.85446009389671362</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0.9478672985781991</v>
+        <v>0.94786729857819907</v>
       </c>
       <c r="B49">
-        <v>0.8199052132701422</v>
+        <v>0.81990521327014221</v>
       </c>
       <c r="C49">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="D49">
-        <v>0.9674418604651163</v>
+        <v>0.96744186046511627</v>
       </c>
       <c r="E49">
-        <v>0.8695652173913043</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="F49">
-        <v>0.8625592417061612</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>0.86255924170616116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.9859154929577465</v>
       </c>
       <c r="B50">
-        <v>0.8104265402843602</v>
+        <v>0.81042654028436023</v>
       </c>
       <c r="C50">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="D50">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="E50">
-        <v>0.9323671497584541</v>
+        <v>0.93236714975845414</v>
       </c>
       <c r="F50">
-        <v>0.8625592417061612</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>0.86255924170616116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.95260663507109</v>
       </c>
       <c r="B51">
-        <v>0.8803827751196173</v>
+        <v>0.88038277511961727</v>
       </c>
       <c r="C51">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="D51">
-        <v>0.9715639810426541</v>
+        <v>0.97156398104265407</v>
       </c>
       <c r="E51">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="F51">
-        <v>0.8840579710144928</v>
+        <v>0.88405797101449279</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2526,7 +2596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1077</v>
       </c>
@@ -2546,7 +2616,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>947</v>
       </c>
@@ -2566,7 +2636,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1050</v>
       </c>
@@ -2586,7 +2656,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1071</v>
       </c>
@@ -2606,7 +2676,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>874</v>
       </c>
@@ -2626,7 +2696,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>775</v>
       </c>
@@ -2646,7 +2716,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>883</v>
       </c>
@@ -2666,7 +2736,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1082</v>
       </c>
@@ -2686,7 +2756,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>818</v>
       </c>
@@ -2706,7 +2776,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>732</v>
       </c>
@@ -2726,7 +2796,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>786</v>
       </c>
@@ -2746,7 +2816,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>845</v>
       </c>
@@ -2766,7 +2836,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>894</v>
       </c>
@@ -2786,7 +2856,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>836</v>
       </c>
@@ -2806,7 +2876,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>992</v>
       </c>
@@ -2826,7 +2896,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>846</v>
       </c>
@@ -2846,7 +2916,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>928</v>
       </c>
@@ -2866,7 +2936,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>820</v>
       </c>
@@ -2886,7 +2956,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1108</v>
       </c>
@@ -2906,7 +2976,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1087</v>
       </c>
@@ -2926,7 +2996,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1011</v>
       </c>
@@ -2946,7 +3016,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1031</v>
       </c>
@@ -2966,7 +3036,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>817</v>
       </c>
@@ -2986,7 +3056,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>872</v>
       </c>
@@ -3006,7 +3076,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>912</v>
       </c>
@@ -3026,7 +3096,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>869</v>
       </c>
@@ -3046,7 +3116,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>868</v>
       </c>
@@ -3066,7 +3136,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>962</v>
       </c>
@@ -3086,7 +3156,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>940</v>
       </c>
@@ -3106,7 +3176,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>822</v>
       </c>
@@ -3126,7 +3196,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>871</v>
       </c>
@@ -3146,7 +3216,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>872</v>
       </c>
@@ -3166,7 +3236,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>763</v>
       </c>
@@ -3186,7 +3256,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>791</v>
       </c>
@@ -3206,7 +3276,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>979</v>
       </c>
@@ -3226,7 +3296,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>845</v>
       </c>
@@ -3246,7 +3316,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>897</v>
       </c>
@@ -3266,7 +3336,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>925</v>
       </c>
@@ -3286,7 +3356,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>650</v>
       </c>
@@ -3306,7 +3376,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>887</v>
       </c>
@@ -3326,7 +3396,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1002</v>
       </c>
@@ -3346,7 +3416,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>912</v>
       </c>
@@ -3366,7 +3436,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>875</v>
       </c>
@@ -3386,7 +3456,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>908</v>
       </c>
@@ -3406,7 +3476,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>967</v>
       </c>
@@ -3426,7 +3496,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>999</v>
       </c>
@@ -3446,7 +3516,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>841</v>
       </c>
@@ -3466,7 +3536,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>902</v>
       </c>
@@ -3486,7 +3556,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>977</v>
       </c>
@@ -3506,7 +3576,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>828</v>
       </c>
@@ -3527,16 +3597,17 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3556,7 +3627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -3577,6 +3648,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>